--- a/data/trans_bre/P1_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P1_R-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 5,5</t>
+          <t>-2,77; 5,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 6,75</t>
+          <t>-3,42; 7,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,58; -0,68</t>
+          <t>-13,13; -1,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 3,65</t>
+          <t>-5,34; 4,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-27,95; 84,68</t>
+          <t>-29,98; 90,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-26,25; 70,78</t>
+          <t>-27,64; 81,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-53,02; -3,97</t>
+          <t>-53,74; -8,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-26,71; 24,47</t>
+          <t>-27,07; 26,15</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,69; -0,3</t>
+          <t>-10,08; -0,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 3,14</t>
+          <t>-5,44; 3,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 7,19</t>
+          <t>-2,0; 7,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 0,07</t>
+          <t>-9,15; 0,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-63,09; -2,38</t>
+          <t>-65,2; -7,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-49,43; 51,39</t>
+          <t>-50,35; 50,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,71; 89,61</t>
+          <t>-16,46; 94,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-42,64; 1,2</t>
+          <t>-42,16; 1,03</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 6,08</t>
+          <t>-2,81; 6,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 8,48</t>
+          <t>-1,12; 7,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 13,76</t>
+          <t>-0,06; 12,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 21,76</t>
+          <t>0,85; 20,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-41,57; 157,65</t>
+          <t>-45,12; 132,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,38; 131,98</t>
+          <t>-11,34; 120,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 146,54</t>
+          <t>-0,33; 139,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 432,55</t>
+          <t>2,21; 336,84</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 3,18</t>
+          <t>-1,55; 3,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,81; -0,78</t>
+          <t>-5,7; -0,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 5,72</t>
+          <t>-0,87; 5,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,18; -3,18</t>
+          <t>-14,23; -3,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,2; 56,7</t>
+          <t>-20,24; 54,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-57,26; -9,62</t>
+          <t>-58,25; -10,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 61,59</t>
+          <t>-7,88; 57,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-70,01; -18,35</t>
+          <t>-67,79; -18,02</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 1,82</t>
+          <t>-5,82; 2,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 5,81</t>
+          <t>-1,26; 6,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 0,23</t>
+          <t>-7,54; 0,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 0,33</t>
+          <t>-10,19; 0,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-48,16; 24,91</t>
+          <t>-46,37; 27,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 97,06</t>
+          <t>-12,38; 93,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-43,17; 2,03</t>
+          <t>-43,46; 1,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-42,1; 1,39</t>
+          <t>-41,78; 2,31</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,3; 10,51</t>
+          <t>5,35; 10,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,42; 12,19</t>
+          <t>6,4; 12,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,26; 9,3</t>
+          <t>0,33; 9,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,85; 19,61</t>
+          <t>6,25; 19,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>106,13; 894,17</t>
+          <t>117,05; 997,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>115,88; 913,19</t>
+          <t>108,73; 975,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,79; 169,37</t>
+          <t>2,51; 153,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26,72; 1063,06</t>
+          <t>33,24; 912,78</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 2,84</t>
+          <t>0,13; 2,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 3,1</t>
+          <t>0,21; 3,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 2,43</t>
+          <t>-0,84; 2,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 3,46</t>
+          <t>-3,28; 3,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,97; 42,35</t>
+          <t>1,01; 41,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,83; 41,9</t>
+          <t>2,21; 40,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 20,95</t>
+          <t>-6,27; 21,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-19,11; 22,9</t>
+          <t>-18,52; 24,69</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P1_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P1_R-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,71</t>
+          <t>-0,21</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-4,12%</t>
+          <t>-1,24%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 5,46</t>
+          <t>-2,31; 5,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 7,33</t>
+          <t>-3,5; 7,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,13; -1,52</t>
+          <t>-12,58; -1,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 4,0</t>
+          <t>-4,36; 4,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-29,98; 90,14</t>
+          <t>-24,19; 96,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-27,64; 81,55</t>
+          <t>-25,74; 75,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-53,74; -8,07</t>
+          <t>-53,12; -6,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-27,07; 26,15</t>
+          <t>-21,96; 28,52</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-4,42</t>
+          <t>-3,96</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-23,82%</t>
+          <t>-21,58%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,08; -0,7</t>
+          <t>-9,68; -0,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 3,29</t>
+          <t>-5,08; 3,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 7,29</t>
+          <t>-1,73; 7,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 0,06</t>
+          <t>-8,51; 0,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-65,2; -7,05</t>
+          <t>-63,0; 0,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-50,35; 50,49</t>
+          <t>-47,38; 50,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,46; 94,63</t>
+          <t>-15,46; 92,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-42,16; 1,03</t>
+          <t>-40,35; 4,07</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,1</t>
+          <t>2,71</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>14,98%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 6,03</t>
+          <t>-3,04; 5,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 7,78</t>
+          <t>-0,75; 8,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 12,97</t>
+          <t>-0,24; 13,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 20,53</t>
+          <t>-3,1; 8,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-45,12; 132,39</t>
+          <t>-48,88; 125,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 120,97</t>
+          <t>-7,49; 143,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 139,02</t>
+          <t>-2,14; 143,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,21; 336,84</t>
+          <t>-15,88; 54,83</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-7,55</t>
+          <t>-5,13</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-39,52%</t>
+          <t>-26,39%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 3,2</t>
+          <t>-1,78; 2,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,7; -0,86</t>
+          <t>-5,63; -0,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 5,32</t>
+          <t>-0,31; 5,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,23; -3,13</t>
+          <t>-8,49; -2,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-20,24; 54,93</t>
+          <t>-23,75; 49,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-58,25; -10,9</t>
+          <t>-56,82; -6,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 57,15</t>
+          <t>-3,27; 58,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-67,79; -18,02</t>
+          <t>-39,09; -10,69</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-4,18</t>
+          <t>-4,55</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-18,29%</t>
+          <t>-18,32%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 2,18</t>
+          <t>-6,15; 2,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 6,0</t>
+          <t>-0,57; 5,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 0,15</t>
+          <t>-7,26; -0,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 0,52</t>
+          <t>-9,11; 0,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-46,37; 27,84</t>
+          <t>-47,3; 29,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,38; 93,76</t>
+          <t>-6,32; 99,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-43,46; 1,26</t>
+          <t>-43,2; 0,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-41,78; 2,31</t>
+          <t>-31,68; 0,46</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15,57</t>
+          <t>15,69</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>313,0%</t>
+          <t>361,91%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,35; 10,39</t>
+          <t>5,19; 10,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,4; 12,43</t>
+          <t>6,26; 12,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 9,06</t>
+          <t>0,96; 9,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,25; 19,21</t>
+          <t>10,94; 19,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>117,05; 997,98</t>
+          <t>102,47; 1024,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>108,73; 975,14</t>
+          <t>108,53; 1032,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,51; 153,17</t>
+          <t>5,94; 152,7</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>33,24; 912,78</t>
+          <t>105,43; 937,35</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,38</t>
+          <t>-0,89</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-2,25%</t>
+          <t>-4,77%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,13; 2,74</t>
+          <t>0,18; 2,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,21; 3,09</t>
+          <t>0,2; 3,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 2,45</t>
+          <t>-1,0; 2,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 3,65</t>
+          <t>-2,84; 0,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 41,15</t>
+          <t>2,15; 41,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,21; 40,55</t>
+          <t>2,1; 42,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 21,16</t>
+          <t>-7,12; 20,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-18,52; 24,69</t>
+          <t>-14,26; 3,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P1_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P1_R-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales</t>
+          <t>Población que conforma un hogar unipersonal</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
